--- a/uploads/dataset2.xlsx
+++ b/uploads/dataset2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a9f76ac732e5fcc/Desktop/ds cell/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C78F9B-AB14-4E4C-9943-FD1D42FE0DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_64756E949257EABF692F4016415DCE3A87426141" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{799F92D8-F28F-424C-B6A5-F9699520F685}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4124,6 +4124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P417"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4187,7 +4188,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4234,7 +4235,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4275,7 +4276,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4322,7 +4323,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4416,7 +4417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4457,7 +4458,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4504,7 +4505,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4586,7 +4587,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4627,7 +4628,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4674,7 +4675,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4715,7 +4716,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4762,7 +4763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4803,7 +4804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4844,7 +4845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4932,7 +4933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5020,7 +5021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5108,7 +5109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5196,7 +5197,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5237,7 +5238,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5278,7 +5279,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5319,7 +5320,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5360,7 +5361,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5401,7 +5402,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5448,7 +5449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5489,7 +5490,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5536,7 +5537,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5583,7 +5584,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5624,7 +5625,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5665,7 +5666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5706,7 +5707,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5747,7 +5748,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5835,7 +5836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5882,7 +5883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5923,7 +5924,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5970,7 +5971,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6011,7 +6012,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6052,7 +6053,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6099,7 +6100,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6140,7 +6141,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6187,7 +6188,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6228,7 +6229,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6275,7 +6276,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6322,7 +6323,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6416,7 +6417,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6463,7 +6464,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6504,7 +6505,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6551,7 +6552,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6686,7 +6687,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6727,7 +6728,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6768,7 +6769,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6809,7 +6810,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6856,7 +6857,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6897,7 +6898,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6938,7 +6939,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6979,7 +6980,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7020,7 +7021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7067,7 +7068,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7149,7 +7150,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7237,7 +7238,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7331,7 +7332,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7378,7 +7379,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7419,7 +7420,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7466,7 +7467,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7513,7 +7514,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7560,7 +7561,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7601,7 +7602,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7642,7 +7643,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7689,7 +7690,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7730,7 +7731,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7771,7 +7772,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7818,7 +7819,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7859,7 +7860,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7900,7 +7901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7941,7 +7942,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7982,7 +7983,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8023,7 +8024,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8064,7 +8065,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8105,7 +8106,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -8199,7 +8200,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -8246,7 +8247,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8287,7 +8288,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8334,7 +8335,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -8375,7 +8376,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -8416,7 +8417,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -8457,7 +8458,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8498,7 +8499,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8539,7 +8540,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8586,7 +8587,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8627,7 +8628,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8668,7 +8669,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8715,7 +8716,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8762,7 +8763,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8803,7 +8804,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8844,7 +8845,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8891,7 +8892,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8938,7 +8939,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8979,7 +8980,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -9020,7 +9021,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -9061,7 +9062,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -9143,7 +9144,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -9184,7 +9185,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -9225,7 +9226,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -9266,7 +9267,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -9313,7 +9314,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -9354,7 +9355,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -9401,7 +9402,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -9442,7 +9443,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -9489,7 +9490,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -9530,7 +9531,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -9577,7 +9578,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -9618,7 +9619,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -9665,7 +9666,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -9706,7 +9707,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -9753,7 +9754,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -9794,7 +9795,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -9835,7 +9836,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -9882,7 +9883,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -9923,7 +9924,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9970,7 +9971,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10011,7 +10012,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10052,7 +10053,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10099,7 +10100,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10146,7 +10147,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10187,7 +10188,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10234,7 +10235,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10275,7 +10276,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10357,7 +10358,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10404,7 +10405,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -10445,7 +10446,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -10492,7 +10493,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -10533,7 +10534,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -10574,7 +10575,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -10662,7 +10663,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -10703,7 +10704,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -10744,7 +10745,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -10791,7 +10792,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -10838,7 +10839,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -10879,7 +10880,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -10920,7 +10921,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -10967,7 +10968,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11008,7 +11009,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11049,7 +11050,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11090,7 +11091,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11137,7 +11138,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11178,7 +11179,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11225,7 +11226,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -11272,7 +11273,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -11319,7 +11320,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -11360,7 +11361,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -11401,7 +11402,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -11442,7 +11443,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -11483,7 +11484,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -11524,7 +11525,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11565,7 +11566,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -11606,7 +11607,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -11653,7 +11654,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -11694,7 +11695,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -11735,7 +11736,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -11776,7 +11777,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11817,7 +11818,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11858,7 +11859,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11899,7 +11900,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11940,7 +11941,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11981,7 +11982,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -12028,7 +12029,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -12069,7 +12070,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -12110,7 +12111,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -12157,7 +12158,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -12198,7 +12199,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -12239,7 +12240,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -12280,7 +12281,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -12327,7 +12328,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -12368,7 +12369,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -12415,7 +12416,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -12462,7 +12463,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -12503,7 +12504,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -12544,7 +12545,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -12591,7 +12592,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -12632,7 +12633,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -12673,7 +12674,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -12714,7 +12715,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -12755,7 +12756,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -12843,7 +12844,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -12884,7 +12885,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -12925,7 +12926,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12972,7 +12973,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -13019,7 +13020,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -13060,7 +13061,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -13107,7 +13108,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -13148,7 +13149,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -13189,7 +13190,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -13230,7 +13231,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -13271,7 +13272,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -13318,7 +13319,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -13359,7 +13360,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -13406,7 +13407,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -13447,7 +13448,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -13494,7 +13495,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -13541,7 +13542,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -13582,7 +13583,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -13623,7 +13624,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -13664,7 +13665,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -13705,7 +13706,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -13746,7 +13747,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -13793,7 +13794,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -13834,7 +13835,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -13881,7 +13882,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -13922,7 +13923,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -13963,7 +13964,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -14004,7 +14005,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -14045,7 +14046,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -14086,7 +14087,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -14133,7 +14134,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -14174,7 +14175,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -14215,7 +14216,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -14256,7 +14257,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -14297,7 +14298,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -14344,7 +14345,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -14385,7 +14386,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -14426,7 +14427,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -14467,7 +14468,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -14508,7 +14509,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -14549,7 +14550,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -14596,7 +14597,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -14637,7 +14638,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -14684,7 +14685,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -14731,7 +14732,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -14772,7 +14773,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -14819,7 +14820,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -14860,7 +14861,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -14948,7 +14949,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -14989,7 +14990,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -15030,7 +15031,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -15071,7 +15072,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -15112,7 +15113,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -15153,7 +15154,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -15194,7 +15195,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -15235,7 +15236,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -15282,7 +15283,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -15329,7 +15330,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -15376,7 +15377,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -15423,7 +15424,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -15464,7 +15465,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -15505,7 +15506,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -15552,7 +15553,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -15593,7 +15594,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -15640,7 +15641,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -15681,7 +15682,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -15722,7 +15723,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -15763,7 +15764,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -15810,7 +15811,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -15851,7 +15852,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -15898,7 +15899,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -15939,7 +15940,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -15986,7 +15987,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -16033,7 +16034,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -16074,7 +16075,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -16115,7 +16116,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -16156,7 +16157,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -16197,7 +16198,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -16238,7 +16239,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -16279,7 +16280,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -16326,7 +16327,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -16373,7 +16374,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -16420,7 +16421,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -16467,7 +16468,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -16514,7 +16515,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -16555,7 +16556,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -16602,7 +16603,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -16649,7 +16650,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -16690,7 +16691,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -16731,7 +16732,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -16772,7 +16773,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -16813,7 +16814,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -16860,7 +16861,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -16948,7 +16949,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -16995,7 +16996,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -17042,7 +17043,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -17083,7 +17084,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -17124,7 +17125,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -17165,7 +17166,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -17206,7 +17207,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -17253,7 +17254,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -17294,7 +17295,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -17341,7 +17342,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -17382,7 +17383,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -17423,7 +17424,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -17464,7 +17465,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -17511,7 +17512,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -17605,7 +17606,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -17652,7 +17653,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -17699,7 +17700,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -17740,7 +17741,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -17781,7 +17782,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -17828,7 +17829,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -17869,7 +17870,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -17910,7 +17911,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -17957,7 +17958,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -17998,7 +17999,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -18039,7 +18040,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>321</v>
       </c>
@@ -18086,7 +18087,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -18127,7 +18128,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -18174,7 +18175,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -18221,7 +18222,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -18262,7 +18263,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>326</v>
       </c>
@@ -18309,7 +18310,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>327</v>
       </c>
@@ -18350,7 +18351,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -18397,7 +18398,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>329</v>
       </c>
@@ -18438,7 +18439,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>330</v>
       </c>
@@ -18479,7 +18480,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -18520,7 +18521,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -18561,7 +18562,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -18608,7 +18609,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -18655,7 +18656,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -18696,7 +18697,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -18737,7 +18738,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>337</v>
       </c>
@@ -18784,7 +18785,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -18831,7 +18832,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -18878,7 +18879,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -18925,7 +18926,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>341</v>
       </c>
@@ -18972,7 +18973,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>342</v>
       </c>
@@ -19013,7 +19014,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>343</v>
       </c>
@@ -19054,7 +19055,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>344</v>
       </c>
@@ -19101,7 +19102,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>345</v>
       </c>
@@ -19148,7 +19149,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>346</v>
       </c>
@@ -19189,7 +19190,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>347</v>
       </c>
@@ -19230,7 +19231,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>348</v>
       </c>
@@ -19271,7 +19272,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>349</v>
       </c>
@@ -19312,7 +19313,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>350</v>
       </c>
@@ -19353,7 +19354,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>351</v>
       </c>
@@ -19394,7 +19395,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>352</v>
       </c>
@@ -19435,7 +19436,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>353</v>
       </c>
@@ -19476,7 +19477,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>354</v>
       </c>
@@ -19517,7 +19518,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>355</v>
       </c>
@@ -19558,7 +19559,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>356</v>
       </c>
@@ -19599,7 +19600,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>357</v>
       </c>
@@ -19640,7 +19641,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>358</v>
       </c>
@@ -19687,7 +19688,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>359</v>
       </c>
@@ -19728,7 +19729,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>360</v>
       </c>
@@ -19816,7 +19817,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>362</v>
       </c>
@@ -19863,7 +19864,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>363</v>
       </c>
@@ -19904,7 +19905,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -19945,7 +19946,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>365</v>
       </c>
@@ -19986,7 +19987,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>366</v>
       </c>
@@ -20033,7 +20034,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>367</v>
       </c>
@@ -20074,7 +20075,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>368</v>
       </c>
@@ -20115,7 +20116,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -20162,7 +20163,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>370</v>
       </c>
@@ -20203,7 +20204,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>371</v>
       </c>
@@ -20244,7 +20245,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>372</v>
       </c>
@@ -20285,7 +20286,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>373</v>
       </c>
@@ -20326,7 +20327,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>374</v>
       </c>
@@ -20373,7 +20374,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>375</v>
       </c>
@@ -20467,7 +20468,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>377</v>
       </c>
@@ -20508,7 +20509,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>378</v>
       </c>
@@ -20549,7 +20550,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>379</v>
       </c>
@@ -20590,7 +20591,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>380</v>
       </c>
@@ -20631,7 +20632,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>381</v>
       </c>
@@ -20678,7 +20679,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>382</v>
       </c>
@@ -20725,7 +20726,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>383</v>
       </c>
@@ -20766,7 +20767,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>384</v>
       </c>
@@ -20807,7 +20808,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>385</v>
       </c>
@@ -20854,7 +20855,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>386</v>
       </c>
@@ -20895,7 +20896,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>387</v>
       </c>
@@ -20942,7 +20943,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>388</v>
       </c>
@@ -20983,7 +20984,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -21024,7 +21025,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>390</v>
       </c>
@@ -21065,7 +21066,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>391</v>
       </c>
@@ -21106,7 +21107,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>392</v>
       </c>
@@ -21147,7 +21148,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>393</v>
       </c>
@@ -21188,7 +21189,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>394</v>
       </c>
@@ -21229,7 +21230,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>395</v>
       </c>
@@ -21270,7 +21271,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>396</v>
       </c>
@@ -21311,7 +21312,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>397</v>
       </c>
@@ -21352,7 +21353,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>398</v>
       </c>
@@ -21393,7 +21394,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>399</v>
       </c>
@@ -21434,7 +21435,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>400</v>
       </c>
@@ -21475,7 +21476,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>401</v>
       </c>
@@ -21522,7 +21523,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>402</v>
       </c>
@@ -21569,7 +21570,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>403</v>
       </c>
@@ -21610,7 +21611,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>404</v>
       </c>
@@ -21657,7 +21658,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>405</v>
       </c>
@@ -21698,7 +21699,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>406</v>
       </c>
@@ -21745,7 +21746,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>407</v>
       </c>
@@ -21786,7 +21787,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -21827,7 +21828,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>409</v>
       </c>
@@ -21868,7 +21869,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>410</v>
       </c>
@@ -21915,7 +21916,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>411</v>
       </c>
@@ -21962,7 +21963,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>412</v>
       </c>
@@ -22003,7 +22004,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>413</v>
       </c>
@@ -22050,7 +22051,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>414</v>
       </c>
@@ -22091,7 +22092,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>415</v>
       </c>
@@ -22132,7 +22133,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -22174,7 +22175,23 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P417" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P417" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BEL1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Aircraft Engine Subsystem"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="12">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>